--- a/submission.xlsx
+++ b/submission.xlsx
@@ -474,7 +474,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.934586</v>
+        <v>0.93412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.878188</v>
+        <v>0.877767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.846864</v>
+        <v>0.846468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.836964</v>
+        <v>0.836417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.81036</v>
+        <v>0.809993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.797855</v>
+        <v>0.797111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.788059</v>
+        <v>0.786311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.785825</v>
+        <v>0.784822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7789740000000001</v>
+        <v>0.778632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.76583</v>
+        <v>0.765888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.757224</v>
+        <v>0.757132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.752542</v>
+        <v>0.752261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.744986</v>
+        <v>0.744671</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.705408</v>
+        <v>0.705125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.703429</v>
+        <v>0.703083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.70137</v>
+        <v>0.7007679999999999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.70056</v>
+        <v>0.700281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.690435</v>
+        <v>0.690164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.690047</v>
+        <v>0.688934</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6877490000000001</v>
+        <v>0.68748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>0.682118</v>
+        <v>0.68125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.679397</v>
+        <v>0.679321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>0.672493</v>
+        <v>0.672175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.664971</v>
+        <v>0.66472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>0.661442</v>
+        <v>0.6611939999999999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.658277</v>
+        <v>0.657805</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6420439999999999</v>
+        <v>0.641811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.636774</v>
+        <v>0.636987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.633732</v>
+        <v>0.633506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>0.62403</v>
+        <v>0.623688</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>0.612228</v>
+        <v>0.612019</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.608497</v>
+        <v>0.608291</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5997400000000001</v>
+        <v>0.5995819999999999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.598275</v>
+        <v>0.597983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>0.592998</v>
+        <v>0.592986</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0.581253</v>
+        <v>0.581068</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.579061</v>
+        <v>0.578879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>0.578697</v>
+        <v>0.578514</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>0.578215</v>
+        <v>0.577634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>0.575508</v>
+        <v>0.575328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>0.573658</v>
+        <v>0.57348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>0.561656</v>
+        <v>0.561487</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0.561505</v>
+        <v>0.5612510000000001</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>0.552502</v>
+        <v>0.552432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>0.55239</v>
+        <v>0.552229</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5477340000000001</v>
+        <v>0.547576</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>0.543474</v>
+        <v>0.543489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>0.523457</v>
+        <v>0.523415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>0.522311</v>
+        <v>0.522174</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>0.516763</v>
+        <v>0.516692</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>0.514116</v>
+        <v>0.514138</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>0.512209</v>
+        <v>0.512039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>0.510269</v>
+        <v>0.510141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>0.508979</v>
+        <v>0.508852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>0.505986</v>
+        <v>0.505861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.503565</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>0.500797</v>
+        <v>0.500677</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>0.500447</v>
+        <v>0.500327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>0.498504</v>
+        <v>0.498451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>0.496517</v>
+        <v>0.496274</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>0.495658</v>
+        <v>0.4955</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>0.493447</v>
+        <v>0.493333</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>0.483447</v>
+        <v>0.483341</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>0.48059</v>
+        <v>0.480486</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>0.480563</v>
+        <v>0.480458</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>0.480531</v>
+        <v>0.48037</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>0.474915</v>
+        <v>0.474815</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>0.472129</v>
+        <v>0.472031</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>0.469417</v>
+        <v>0.469322</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>0.465607</v>
+        <v>0.465625</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>0.464368</v>
+        <v>0.464388</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>0.460115</v>
+        <v>0.459855</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>0.455273</v>
+        <v>0.455398</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>0.447857</v>
+        <v>0.447779</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>0.440961</v>
+        <v>0.441016</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>0.436046</v>
+        <v>0.435977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>0.421882</v>
+        <v>0.421825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>0.416869</v>
+        <v>0.416816</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>0.412985</v>
+        <v>0.412846</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>0.402051</v>
+        <v>0.402128</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>0.399643</v>
+        <v>0.399604</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>0.399041</v>
+        <v>0.399186</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>0.398728</v>
+        <v>0.398876</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>0.394493</v>
+        <v>0.394649</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>0.384571</v>
+        <v>0.384605</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -1997,36 +1997,36 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAND_0079284</t>
+          <t>CAND_0030953</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>0.383453</v>
+        <v>0.383443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4.9y experience as Machine Learning Engineer at Google; career evidence shows shipped search/ranking/retrieval or matching systems; mostly product-company background; has pre-LLM-era ranking/retrieval evidence</t>
+          <t>7.8y experience as Search Engineer at Nykaa; career evidence shows shipped search/ranking/retrieval or matching systems; mostly product-company background; has pre-LLM-era ranking/retrieval evidence</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAND_0030953</t>
+          <t>CAND_0079284</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>0.383393</v>
+        <v>0.383426</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7.8y experience as Search Engineer at Nykaa; career evidence shows shipped search/ranking/retrieval or matching systems; mostly product-company background; has pre-LLM-era ranking/retrieval evidence</t>
+          <t>4.9y experience as Machine Learning Engineer at Google; career evidence shows shipped search/ranking/retrieval or matching systems; mostly product-company background; has pre-LLM-era ranking/retrieval evidence</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>0.378136</v>
+        <v>0.378171</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>0.377092</v>
+        <v>0.377146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>0.374768</v>
+        <v>0.375119</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>0.372721</v>
+        <v>0.372703</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>0.363023</v>
+        <v>0.362898</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>0.361753</v>
+        <v>0.361743</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>0.360588</v>
+        <v>0.36085</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>0.355424</v>
+        <v>0.355323</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>97</v>
       </c>
       <c r="C98" t="n">
-        <v>0.354663</v>
+        <v>0.354566</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>98</v>
       </c>
       <c r="C99" t="n">
-        <v>0.354168</v>
+        <v>0.354251</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>0.350905</v>
+        <v>0.350993</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
